--- a/ssp_modeling/transformations/templates/calibrated/libya/model_input_variables_libya_af_calibrated.xlsx
+++ b/ssp_modeling/transformations/templates/calibrated/libya/model_input_variables_libya_af_calibrated.xlsx
@@ -91292,7 +91292,7 @@
         <v>0.9806062523638095</v>
       </c>
       <c r="AD39">
-        <v>0.980614221161378</v>
+        <v>0.9806142211613781</v>
       </c>
       <c r="AE39">
         <v>0.9806229190151031</v>
@@ -91313,7 +91313,7 @@
         <v>0.980677198885849</v>
       </c>
       <c r="AK39">
-        <v>0.9806901868752251</v>
+        <v>0.980690186875225</v>
       </c>
       <c r="AL39">
         <v>0.9807038776664154</v>
@@ -91399,67 +91399,67 @@
         <v>0.002042770894366918</v>
       </c>
       <c r="X40">
-        <v>0.001313605379174832</v>
+        <v>0.001313605379174847</v>
       </c>
       <c r="Y40">
-        <v>0.0013092793012192</v>
+        <v>0.001309279301219194</v>
       </c>
       <c r="Z40">
-        <v>0.001304183796921382</v>
+        <v>0.001304183796921401</v>
       </c>
       <c r="AA40">
-        <v>0.001298324970323611</v>
+        <v>0.001298324970323602</v>
       </c>
       <c r="AB40">
-        <v>0.001291708526765196</v>
+        <v>0.00129170852676521</v>
       </c>
       <c r="AC40">
-        <v>0.001284339812887216</v>
+        <v>0.001284339812887231</v>
       </c>
       <c r="AD40">
-        <v>0.00127622385104693</v>
+        <v>0.00127622385104692</v>
       </c>
       <c r="AE40">
-        <v>0.00126736536915945</v>
+        <v>0.001267365369159483</v>
       </c>
       <c r="AF40">
-        <v>0.001257768826795099</v>
+        <v>0.001257768826795117</v>
       </c>
       <c r="AG40">
-        <v>0.001247438438246254</v>
+        <v>0.001247438438246253</v>
       </c>
       <c r="AH40">
-        <v>0.001236378193204689</v>
+        <v>0.001236378193204703</v>
       </c>
       <c r="AI40">
-        <v>0.001224591875643199</v>
+        <v>0.001224591875643203</v>
       </c>
       <c r="AJ40">
         <v>0.001212083081476577</v>
       </c>
       <c r="AK40">
-        <v>0.001198855235587431</v>
+        <v>0.00119885523558744</v>
       </c>
       <c r="AL40">
-        <v>0.001184911608847185</v>
+        <v>0.001184911608847176</v>
       </c>
       <c r="AM40">
-        <v>0.001170256576452036</v>
+        <v>0.001170256576452055</v>
       </c>
       <c r="AN40">
-        <v>0.001154897426782163</v>
+        <v>0.001154897426782154</v>
       </c>
       <c r="AO40">
-        <v>0.001138832287398536</v>
+        <v>0.001138832287398545</v>
       </c>
       <c r="AP40">
         <v>0.001122064360068355</v>
       </c>
       <c r="AQ40">
-        <v>0.001104596810479935</v>
+        <v>0.001104596810479944</v>
       </c>
       <c r="AR40">
-        <v>0.001086432810097126</v>
+        <v>0.001086432810097145</v>
       </c>
       <c r="AS40">
         <v>0</v>
@@ -91542,7 +91542,7 @@
         <v>0.008837950766437794</v>
       </c>
       <c r="AD41">
-        <v>0.008838022587151162</v>
+        <v>0.008838022587151164</v>
       </c>
       <c r="AE41">
         <v>0.008838100978659284</v>
@@ -91563,7 +91563,7 @@
         <v>0.008838590189108538</v>
       </c>
       <c r="AK41">
-        <v>0.008838707246500724</v>
+        <v>0.008838707246500722</v>
       </c>
       <c r="AL41">
         <v>0.008838830638064055</v>
@@ -91688,7 +91688,7 @@
         <v>0.009272127843565878</v>
       </c>
       <c r="AK42">
-        <v>0.009272250642686795</v>
+        <v>0.009272250642686794</v>
       </c>
       <c r="AL42">
         <v>0.0092723800866734</v>
@@ -92170,13 +92170,13 @@
         <v>0.0013654798833158</v>
       </c>
       <c r="AE46">
-        <v>0.001365479883315801</v>
+        <v>0.0013654798833158</v>
       </c>
       <c r="AF46">
         <v>0.0013654798833158</v>
       </c>
       <c r="AG46">
-        <v>0.001365479883315801</v>
+        <v>0.0013654798833158</v>
       </c>
       <c r="AH46">
         <v>0.0013654798833158</v>
@@ -92203,7 +92203,7 @@
         <v>0.001364231540956815</v>
       </c>
       <c r="AP46">
-        <v>0.001363662995107851</v>
+        <v>0.00136366299510785</v>
       </c>
       <c r="AQ46">
         <v>0.001363094922946404</v>
@@ -93155,34 +93155,34 @@
         <v>0.001064344956902613</v>
       </c>
       <c r="Z54">
-        <v>0.001011128933645818</v>
+        <v>0.001011128933645817</v>
       </c>
       <c r="AA54">
         <v>0.0009579129103890218</v>
       </c>
       <c r="AB54">
-        <v>0.0009046968871322262</v>
+        <v>0.0009046968871322261</v>
       </c>
       <c r="AC54">
         <v>0.0008514808638754307</v>
       </c>
       <c r="AD54">
-        <v>0.0007982648406186349</v>
+        <v>0.0007982648406186348</v>
       </c>
       <c r="AE54">
-        <v>0.0007450488173618396</v>
+        <v>0.0007450488173618393</v>
       </c>
       <c r="AF54">
-        <v>0.0006918327941050437</v>
+        <v>0.0006918327941050434</v>
       </c>
       <c r="AG54">
-        <v>0.000638616770848248</v>
+        <v>0.0006386167708482476</v>
       </c>
       <c r="AH54">
-        <v>0.0005854007475914516</v>
+        <v>0.0005854007475914513</v>
       </c>
       <c r="AI54">
-        <v>0.0005321847243346567</v>
+        <v>0.0005321847243346566</v>
       </c>
       <c r="AJ54">
         <v>0.0004789687010778606</v>
@@ -93194,25 +93194,25 @@
         <v>0.0003725366545642698</v>
       </c>
       <c r="AM54">
-        <v>0.0003193206313074736</v>
+        <v>0.0003193206313074737</v>
       </c>
       <c r="AN54">
         <v>0.0002661046080506777</v>
       </c>
       <c r="AO54">
-        <v>0.0002128885847938828</v>
+        <v>0.0002128885847938827</v>
       </c>
       <c r="AP54">
-        <v>0.0001596725615370868</v>
+        <v>0.0001596725615370867</v>
       </c>
       <c r="AQ54">
         <v>0.0001064565382802907</v>
       </c>
       <c r="AR54">
-        <v>5.324051502349571E-05</v>
+        <v>5.324051502349574E-05</v>
       </c>
       <c r="AS54">
-        <v>2.445073394212432E-08</v>
+        <v>2.445073394212431E-08</v>
       </c>
     </row>
     <row r="55" spans="1:45">
@@ -93771,73 +93771,73 @@
         <v>0.002087220241380529</v>
       </c>
       <c r="W59">
-        <v>0.001996585202198347</v>
+        <v>0.001996585202198405</v>
       </c>
       <c r="X59">
-        <v>0.001905950163016426</v>
+        <v>0.001905950163016483</v>
       </c>
       <c r="Y59">
-        <v>0.001815315123834215</v>
+        <v>0.00181531512383436</v>
       </c>
       <c r="Z59">
-        <v>0.001724680084652177</v>
+        <v>0.001724680084652206</v>
       </c>
       <c r="AA59">
         <v>0.001634045045470053</v>
       </c>
       <c r="AB59">
-        <v>0.001543410006288045</v>
+        <v>0.001543410006288074</v>
       </c>
       <c r="AC59">
         <v>0.00145277496710595</v>
       </c>
       <c r="AD59">
-        <v>0.001362139927923825</v>
+        <v>0.001362139927923883</v>
       </c>
       <c r="AE59">
-        <v>0.001271504888741759</v>
+        <v>0.001271504888741817</v>
       </c>
       <c r="AF59">
-        <v>0.001180869849559606</v>
+        <v>0.001180869849559693</v>
       </c>
       <c r="AG59">
-        <v>0.001090234810377453</v>
+        <v>0.001090234810377627</v>
       </c>
       <c r="AH59">
-        <v>0.0009995997711954444</v>
+        <v>0.0009995997711955027</v>
       </c>
       <c r="AI59">
-        <v>0.0009089647320133783</v>
+        <v>0.0009089647320134365</v>
       </c>
       <c r="AJ59">
         <v>0.0008183296928313411</v>
       </c>
       <c r="AK59">
-        <v>0.000727694653649304</v>
+        <v>0.0007276946536493331</v>
       </c>
       <c r="AL59">
         <v>0.0006370596144671506</v>
       </c>
       <c r="AM59">
-        <v>0.0005464245752852004</v>
+        <v>0.0005464245752851135</v>
       </c>
       <c r="AN59">
         <v>0.0004557895361030474</v>
       </c>
       <c r="AO59">
-        <v>0.000365154496920865</v>
+        <v>0.0003651544969209811</v>
       </c>
       <c r="AP59">
-        <v>0.0002745194577387698</v>
+        <v>0.0002745194577389149</v>
       </c>
       <c r="AQ59">
-        <v>0.0001838844185567617</v>
+        <v>0.0001838844185567326</v>
       </c>
       <c r="AR59">
-        <v>9.32493793747535E-05</v>
+        <v>9.324937937463739E-05</v>
       </c>
       <c r="AS59">
-        <v>0.0004406085386007884</v>
+        <v>0.0004406085386008754</v>
       </c>
     </row>
     <row r="60" spans="1:45">
@@ -93896,40 +93896,40 @@
         <v>0.992016263808115</v>
       </c>
       <c r="W60">
-        <v>0.9923629479903713</v>
+        <v>0.9923629479903711</v>
       </c>
       <c r="X60">
-        <v>0.9927096321726265</v>
+        <v>0.9927096321726261</v>
       </c>
       <c r="Y60">
-        <v>0.9930563163548829</v>
+        <v>0.9930563163548822</v>
       </c>
       <c r="Z60">
-        <v>0.9934030005371386</v>
+        <v>0.9934030005371385</v>
       </c>
       <c r="AA60">
         <v>0.9937496847193946</v>
       </c>
       <c r="AB60">
-        <v>0.9940963689016502</v>
+        <v>0.9940963689016501</v>
       </c>
       <c r="AC60">
         <v>0.9944430530839061</v>
       </c>
       <c r="AD60">
-        <v>0.9947897372661622</v>
+        <v>0.9947897372661618</v>
       </c>
       <c r="AE60">
-        <v>0.995136421448418</v>
+        <v>0.9951364214484177</v>
       </c>
       <c r="AF60">
-        <v>0.9954831056306741</v>
+        <v>0.9954831056306737</v>
       </c>
       <c r="AG60">
-        <v>0.9958297898129302</v>
+        <v>0.9958297898129296</v>
       </c>
       <c r="AH60">
-        <v>0.9961764739951857</v>
+        <v>0.9961764739951856</v>
       </c>
       <c r="AI60">
         <v>0.9965231581774414</v>
@@ -93938,31 +93938,31 @@
         <v>0.9968698423596972</v>
       </c>
       <c r="AK60">
-        <v>0.997216526541953</v>
+        <v>0.9972165265419529</v>
       </c>
       <c r="AL60">
         <v>0.9975632107242092</v>
       </c>
       <c r="AM60">
-        <v>0.9979098949064645</v>
+        <v>0.9979098949064649</v>
       </c>
       <c r="AN60">
         <v>0.9982565790887207</v>
       </c>
       <c r="AO60">
-        <v>0.9986032632709769</v>
+        <v>0.9986032632709765</v>
       </c>
       <c r="AP60">
-        <v>0.9989499474532328</v>
+        <v>0.9989499474532323</v>
       </c>
       <c r="AQ60">
-        <v>0.9992966316354884</v>
+        <v>0.9992966316354885</v>
       </c>
       <c r="AR60">
-        <v>0.999643315817744</v>
+        <v>0.9996433158177445</v>
       </c>
       <c r="AS60">
-        <v>0.9983146472680076</v>
+        <v>0.9983146472680072</v>
       </c>
     </row>
     <row r="61" spans="1:45">
@@ -94021,73 +94021,73 @@
         <v>0.002300189258296732</v>
       </c>
       <c r="W61">
-        <v>0.002200306294621434</v>
+        <v>0.002200306294621498</v>
       </c>
       <c r="X61">
-        <v>0.002100423330946423</v>
+        <v>0.002100423330946486</v>
       </c>
       <c r="Y61">
-        <v>0.002000540367271093</v>
+        <v>0.002000540367271252</v>
       </c>
       <c r="Z61">
-        <v>0.001900657403595954</v>
+        <v>0.001900657403595986</v>
       </c>
       <c r="AA61">
         <v>0.001800774439920719</v>
       </c>
       <c r="AB61">
-        <v>0.001700891476245613</v>
+        <v>0.001700891476245645</v>
       </c>
       <c r="AC61">
         <v>0.00160100851257041</v>
       </c>
       <c r="AD61">
-        <v>0.001501125548895176</v>
+        <v>0.001501125548895239</v>
       </c>
       <c r="AE61">
-        <v>0.001401242585220005</v>
+        <v>0.001401242585220069</v>
       </c>
       <c r="AF61">
-        <v>0.001301359621544739</v>
+        <v>0.001301359621544835</v>
       </c>
       <c r="AG61">
-        <v>0.001201476657869472</v>
+        <v>0.001201476657869664</v>
       </c>
       <c r="AH61">
-        <v>0.001101593694194366</v>
+        <v>0.00110159369419443</v>
       </c>
       <c r="AI61">
-        <v>0.001001710730519195</v>
+        <v>0.001001710730519259</v>
       </c>
       <c r="AJ61">
         <v>0.0009018277668440564</v>
       </c>
       <c r="AK61">
-        <v>0.0008019448031689179</v>
+        <v>0.00080194480316895</v>
       </c>
       <c r="AL61">
         <v>0.0007020618394936513</v>
       </c>
       <c r="AM61">
-        <v>0.0006021788758186086</v>
+        <v>0.0006021788758185127</v>
       </c>
       <c r="AN61">
         <v>0.0005022959121433423</v>
       </c>
       <c r="AO61">
-        <v>0.0004024129484680438</v>
+        <v>0.0004024129484681717</v>
       </c>
       <c r="AP61">
-        <v>0.0003025299847928412</v>
+        <v>0.0003025299847930012</v>
       </c>
       <c r="AQ61">
-        <v>0.0002026470211177347</v>
+        <v>0.0002026470211177027</v>
       </c>
       <c r="AR61">
-        <v>0.0001027640574426281</v>
+        <v>0.0001027640574425002</v>
       </c>
       <c r="AS61">
-        <v>0.0004855659252005991</v>
+        <v>0.000485565925200695</v>
       </c>
     </row>
     <row r="62" spans="1:45">
@@ -94146,73 +94146,73 @@
         <v>0.00359632669220775</v>
       </c>
       <c r="W62">
-        <v>0.00344016051280898</v>
+        <v>0.00344016051280908</v>
       </c>
       <c r="X62">
-        <v>0.003283994333410659</v>
+        <v>0.003283994333410757</v>
       </c>
       <c r="Y62">
-        <v>0.003127828154011838</v>
+        <v>0.003127828154012087</v>
       </c>
       <c r="Z62">
-        <v>0.002971661974613317</v>
+        <v>0.002971661974613367</v>
       </c>
       <c r="AA62">
         <v>0.002815495795214646</v>
       </c>
       <c r="AB62">
-        <v>0.002659329615816175</v>
+        <v>0.002659329615816225</v>
       </c>
       <c r="AC62">
         <v>0.002503163436417555</v>
       </c>
       <c r="AD62">
-        <v>0.002346997257018883</v>
+        <v>0.002346997257018983</v>
       </c>
       <c r="AE62">
-        <v>0.002190831077620312</v>
+        <v>0.002190831077620413</v>
       </c>
       <c r="AF62">
-        <v>0.002034664898221592</v>
+        <v>0.002034664898221743</v>
       </c>
       <c r="AG62">
-        <v>0.001878498718822871</v>
+        <v>0.001878498718823171</v>
       </c>
       <c r="AH62">
-        <v>0.0017223325394244</v>
+        <v>0.001722332539424501</v>
       </c>
       <c r="AI62">
-        <v>0.001566166360025829</v>
+        <v>0.00156616636002593</v>
       </c>
       <c r="AJ62">
         <v>0.001410000180627309</v>
       </c>
       <c r="AK62">
-        <v>0.001253834001228788</v>
+        <v>0.001253834001228838</v>
       </c>
       <c r="AL62">
         <v>0.001097667821830067</v>
       </c>
       <c r="AM62">
-        <v>0.0009415016424316962</v>
+        <v>0.0009415016424315463</v>
       </c>
       <c r="AN62">
         <v>0.0007853354630329757</v>
       </c>
       <c r="AO62">
-        <v>0.0006291692836342047</v>
+        <v>0.0006291692836344049</v>
       </c>
       <c r="AP62">
-        <v>0.0004730031042355839</v>
+        <v>0.000473003104235834</v>
       </c>
       <c r="AQ62">
-        <v>0.0003168369248371133</v>
+        <v>0.0003168369248370632</v>
       </c>
       <c r="AR62">
-        <v>0.0001606707454386425</v>
+        <v>0.0001606707454384424</v>
       </c>
       <c r="AS62">
-        <v>0.0007591782681910924</v>
+        <v>0.0007591782681912423</v>
       </c>
     </row>
     <row r="63" spans="1:45">
@@ -94271,37 +94271,37 @@
         <v>0.1041884631582289</v>
       </c>
       <c r="W63">
-        <v>0.09820684083611543</v>
+        <v>0.0982068408361154</v>
       </c>
       <c r="X63">
         <v>0.1040076182141184</v>
       </c>
       <c r="Y63">
-        <v>0.1040111631965932</v>
+        <v>0.104011163196593</v>
       </c>
       <c r="Z63">
         <v>0.1040146418393949</v>
       </c>
       <c r="AA63">
-        <v>0.1040180639392472</v>
+        <v>0.1040180639392471</v>
       </c>
       <c r="AB63">
-        <v>0.1040214381056073</v>
+        <v>0.1040214381056074</v>
       </c>
       <c r="AC63">
         <v>0.1040247719347693</v>
       </c>
       <c r="AD63">
-        <v>0.1040280721574153</v>
+        <v>0.1040280721574152</v>
       </c>
       <c r="AE63">
-        <v>0.104031344763744</v>
+        <v>0.1040313447637441</v>
       </c>
       <c r="AF63">
         <v>0.1040345951096772</v>
       </c>
       <c r="AG63">
-        <v>0.1040378280071023</v>
+        <v>0.1040378280071022</v>
       </c>
       <c r="AH63">
         <v>0.1040410478006594</v>
@@ -94316,25 +94316,25 @@
         <v>0.1040506663044501</v>
       </c>
       <c r="AL63">
-        <v>0.1040538698834402</v>
+        <v>0.10405386988344</v>
       </c>
       <c r="AM63">
-        <v>0.1040570770558948</v>
+        <v>0.1040570770558949</v>
       </c>
       <c r="AN63">
         <v>0.1040602914004937</v>
       </c>
       <c r="AO63">
-        <v>0.1040635193047277</v>
+        <v>0.1040635193047276</v>
       </c>
       <c r="AP63">
-        <v>0.1040667624413963</v>
+        <v>0.1040667624413961</v>
       </c>
       <c r="AQ63">
         <v>0.1040700224268922</v>
       </c>
       <c r="AR63">
-        <v>0.1040733008267346</v>
+        <v>0.1040733008267349</v>
       </c>
       <c r="AS63">
         <v>0.1041732159797497</v>
@@ -94396,40 +94396,40 @@
         <v>0.002124544769375</v>
       </c>
       <c r="W64">
-        <v>0.05941413247191916</v>
+        <v>0.05941413247191937</v>
       </c>
       <c r="X64">
-        <v>0.003856605359004775</v>
+        <v>0.003856605359004774</v>
       </c>
       <c r="Y64">
-        <v>0.003822652933816517</v>
+        <v>0.00382265293381841</v>
       </c>
       <c r="Z64">
-        <v>0.0037893358835017</v>
+        <v>0.003789335883500999</v>
       </c>
       <c r="AA64">
-        <v>0.003756560378954813</v>
+        <v>0.00375656037895551</v>
       </c>
       <c r="AB64">
-        <v>0.003724243962236576</v>
+        <v>0.003724243962236119</v>
       </c>
       <c r="AC64">
-        <v>0.003692313879079302</v>
+        <v>0.003692313879078621</v>
       </c>
       <c r="AD64">
-        <v>0.003660705665698847</v>
+        <v>0.003660705665700201</v>
       </c>
       <c r="AE64">
-        <v>0.003629361950367528</v>
+        <v>0.003629361950366413</v>
       </c>
       <c r="AF64">
-        <v>0.003598231436207217</v>
+        <v>0.003598231436207215</v>
       </c>
       <c r="AG64">
-        <v>0.003567268036882197</v>
+        <v>0.003567268036883513</v>
       </c>
       <c r="AH64">
-        <v>0.003536430141167205</v>
+        <v>0.003536430141167203</v>
       </c>
       <c r="AI64">
         <v>0.003505679986226059</v>
@@ -94438,31 +94438,31 @@
         <v>0.003474983122581718</v>
       </c>
       <c r="AK64">
-        <v>0.003444307956447428</v>
+        <v>0.003444307956447001</v>
       </c>
       <c r="AL64">
-        <v>0.003413625357374603</v>
+        <v>0.003413625357375872</v>
       </c>
       <c r="AM64">
-        <v>0.003382908341535092</v>
+        <v>0.003382908341533835</v>
       </c>
       <c r="AN64">
-        <v>0.003352122633763898</v>
+        <v>0.003352122633764315</v>
       </c>
       <c r="AO64">
-        <v>0.003321207057227781</v>
+        <v>0.003321207057228194</v>
       </c>
       <c r="AP64">
-        <v>0.003290145590521374</v>
+        <v>0.003290145590523432</v>
       </c>
       <c r="AQ64">
-        <v>0.00325892275248212</v>
+        <v>0.003258922752482124</v>
       </c>
       <c r="AR64">
-        <v>0.003227523549191875</v>
+        <v>0.003227523549189436</v>
       </c>
       <c r="AS64">
-        <v>0.002270576150439033</v>
+        <v>0.002270576150438629</v>
       </c>
     </row>
     <row r="65" spans="1:45">
@@ -94521,37 +94521,37 @@
         <v>0.8762267779987492</v>
       </c>
       <c r="W65">
-        <v>0.8259212307660283</v>
+        <v>0.8259212307660281</v>
       </c>
       <c r="X65">
         <v>0.8747058688895066</v>
       </c>
       <c r="Y65">
-        <v>0.874735682253461</v>
+        <v>0.8747356822534593</v>
       </c>
       <c r="Z65">
-        <v>0.8747649376996159</v>
+        <v>0.8747649376996163</v>
       </c>
       <c r="AA65">
-        <v>0.8747937176185886</v>
+        <v>0.8747937176185878</v>
       </c>
       <c r="AB65">
-        <v>0.8748220944160627</v>
+        <v>0.8748220944160632</v>
       </c>
       <c r="AC65">
-        <v>0.8748501319770022</v>
+        <v>0.8748501319770028</v>
       </c>
       <c r="AD65">
-        <v>0.8748778869065613</v>
+        <v>0.8748778869065602</v>
       </c>
       <c r="AE65">
-        <v>0.8749054095824137</v>
+        <v>0.8749054095824147</v>
       </c>
       <c r="AF65">
         <v>0.8749327450479542</v>
       </c>
       <c r="AG65">
-        <v>0.8749599337712404</v>
+        <v>0.8749599337712392</v>
       </c>
       <c r="AH65">
         <v>0.87498701229077</v>
@@ -94563,31 +94563,31 @@
         <v>0.8750409684461505</v>
       </c>
       <c r="AK65">
-        <v>0.8750679040740843</v>
+        <v>0.8750679040740846</v>
       </c>
       <c r="AL65">
-        <v>0.8750948462288245</v>
+        <v>0.8750948462288234</v>
       </c>
       <c r="AM65">
-        <v>0.8751218186046633</v>
+        <v>0.8751218186046644</v>
       </c>
       <c r="AN65">
-        <v>0.8751488512983601</v>
+        <v>0.8751488512983597</v>
       </c>
       <c r="AO65">
-        <v>0.8751759980288225</v>
+        <v>0.8751759980288221</v>
       </c>
       <c r="AP65">
-        <v>0.8752032728643236</v>
+        <v>0.8752032728643218</v>
       </c>
       <c r="AQ65">
         <v>0.8752306893987536</v>
       </c>
       <c r="AR65">
-        <v>0.8752582607981567</v>
+        <v>0.8752582607981588</v>
       </c>
       <c r="AS65">
-        <v>0.8760985489639075</v>
+        <v>0.8760985489639078</v>
       </c>
     </row>
     <row r="66" spans="1:45">
@@ -94652,31 +94652,31 @@
         <v>0.01630700632464488</v>
       </c>
       <c r="Y66">
-        <v>0.01630756213058132</v>
+        <v>0.01630756213058128</v>
       </c>
       <c r="Z66">
         <v>0.01630810753534245</v>
       </c>
       <c r="AA66">
-        <v>0.01630864407492381</v>
+        <v>0.01630864407492379</v>
       </c>
       <c r="AB66">
-        <v>0.01630917309917338</v>
+        <v>0.01630917309917339</v>
       </c>
       <c r="AC66">
-        <v>0.01630969579908866</v>
+        <v>0.01630969579908867</v>
       </c>
       <c r="AD66">
-        <v>0.01631021322995081</v>
+        <v>0.01631021322995078</v>
       </c>
       <c r="AE66">
-        <v>0.01631072633094299</v>
+        <v>0.01631072633094301</v>
       </c>
       <c r="AF66">
         <v>0.01631123594180226</v>
       </c>
       <c r="AG66">
-        <v>0.01631174281696837</v>
+        <v>0.01631174281696834</v>
       </c>
       <c r="AH66">
         <v>0.01631224763762287</v>
@@ -94688,28 +94688,28 @@
         <v>0.01631325353388851</v>
       </c>
       <c r="AK66">
-        <v>0.01631375569063707</v>
+        <v>0.01631375569063708</v>
       </c>
       <c r="AL66">
-        <v>0.01631425796906388</v>
+        <v>0.01631425796906386</v>
       </c>
       <c r="AM66">
-        <v>0.01631476081089796</v>
+        <v>0.01631476081089799</v>
       </c>
       <c r="AN66">
-        <v>0.01631526477722855</v>
+        <v>0.01631526477722854</v>
       </c>
       <c r="AO66">
-        <v>0.01631577086952893</v>
+        <v>0.01631577086952892</v>
       </c>
       <c r="AP66">
-        <v>0.01631627935007175</v>
+        <v>0.01631627935007172</v>
       </c>
       <c r="AQ66">
         <v>0.0163167904722858</v>
       </c>
       <c r="AR66">
-        <v>0.01631730448162361</v>
+        <v>0.01631730448162365</v>
       </c>
       <c r="AS66">
         <v>0.01633296984402803</v>
@@ -94771,37 +94771,37 @@
         <v>0.0011248536755406</v>
       </c>
       <c r="W67">
-        <v>0.001060274069979986</v>
+        <v>0.001060274069979985</v>
       </c>
       <c r="X67">
         <v>0.001122901212725435</v>
       </c>
       <c r="Y67">
-        <v>0.001122939485548026</v>
+        <v>0.001122939485548024</v>
       </c>
       <c r="Z67">
-        <v>0.001122977042145203</v>
+        <v>0.001122977042145204</v>
       </c>
       <c r="AA67">
-        <v>0.00112301398828569</v>
+        <v>0.001123013988285689</v>
       </c>
       <c r="AB67">
-        <v>0.00112305041692008</v>
+        <v>0.001123050416920081</v>
       </c>
       <c r="AC67">
-        <v>0.001123086410060518</v>
+        <v>0.001123086410060519</v>
       </c>
       <c r="AD67">
-        <v>0.001123122040373712</v>
+        <v>0.001123122040373711</v>
       </c>
       <c r="AE67">
-        <v>0.001123157372531859</v>
+        <v>0.001123157372531861</v>
       </c>
       <c r="AF67">
         <v>0.001123192464359293</v>
       </c>
       <c r="AG67">
-        <v>0.001123227367806767</v>
+        <v>0.001123227367806766</v>
       </c>
       <c r="AH67">
         <v>0.001123262129780478</v>
@@ -94813,31 +94813,31 @@
         <v>0.001123331395844038</v>
       </c>
       <c r="AK67">
-        <v>0.001123365974381061</v>
+        <v>0.001123365974381062</v>
       </c>
       <c r="AL67">
-        <v>0.001123400561296855</v>
+        <v>0.001123400561296853</v>
       </c>
       <c r="AM67">
-        <v>0.001123435187008899</v>
+        <v>0.0011234351870089</v>
       </c>
       <c r="AN67">
-        <v>0.001123469890153825</v>
+        <v>0.001123469890153824</v>
       </c>
       <c r="AO67">
         <v>0.001123504739693129</v>
       </c>
       <c r="AP67">
-        <v>0.001123539753686919</v>
+        <v>0.001123539753686916</v>
       </c>
       <c r="AQ67">
         <v>0.001123574949586312</v>
       </c>
       <c r="AR67">
-        <v>0.001123610344293181</v>
+        <v>0.001123610344293184</v>
       </c>
       <c r="AS67">
-        <v>0.001124689061875765</v>
+        <v>0.001124689061875766</v>
       </c>
     </row>
     <row r="68" spans="1:45">
@@ -95024,67 +95024,67 @@
         <v>0.0001571698241325078</v>
       </c>
       <c r="X69">
-        <v>0.0001010681750918568</v>
+        <v>0.0001010681750918579</v>
       </c>
       <c r="Y69">
-        <v>0.0001007353287049491</v>
+        <v>0.0001007353287049487</v>
       </c>
       <c r="Z69">
-        <v>0.0001003432830200596</v>
+        <v>0.0001003432830200611</v>
       </c>
       <c r="AA69">
-        <v>9.989250767930368E-05</v>
+        <v>9.989250767930293E-05</v>
       </c>
       <c r="AB69">
-        <v>9.938344164878289E-05</v>
+        <v>9.938344164878397E-05</v>
       </c>
       <c r="AC69">
-        <v>9.881649629652701E-05</v>
+        <v>9.881649629652815E-05</v>
       </c>
       <c r="AD69">
-        <v>9.819205804032245E-05</v>
+        <v>9.819205804032171E-05</v>
       </c>
       <c r="AE69">
-        <v>9.751049064371643E-05</v>
+        <v>9.751049064371899E-05</v>
       </c>
       <c r="AF69">
-        <v>9.677213722393527E-05</v>
+        <v>9.67721372239367E-05</v>
       </c>
       <c r="AG69">
-        <v>9.597732202663647E-05</v>
+        <v>9.59773220266364E-05</v>
       </c>
       <c r="AH69">
-        <v>9.512635201681366E-05</v>
+        <v>9.512635201681474E-05</v>
       </c>
       <c r="AI69">
-        <v>9.421951833153962E-05</v>
+        <v>9.421951833153998E-05</v>
       </c>
       <c r="AJ69">
         <v>9.325709763879376E-05</v>
       </c>
       <c r="AK69">
-        <v>9.223935344742014E-05</v>
+        <v>9.223935344742086E-05</v>
       </c>
       <c r="AL69">
-        <v>9.11665374167155E-05</v>
+        <v>9.116653741671478E-05</v>
       </c>
       <c r="AM69">
-        <v>9.003898617220081E-05</v>
+        <v>9.003898617220228E-05</v>
       </c>
       <c r="AN69">
-        <v>8.885726047839171E-05</v>
+        <v>8.885726047839099E-05</v>
       </c>
       <c r="AO69">
-        <v>8.762121627071686E-05</v>
+        <v>8.762121627071756E-05</v>
       </c>
       <c r="AP69">
-        <v>8.633109989162685E-05</v>
+        <v>8.633109989162681E-05</v>
       </c>
       <c r="AQ69">
-        <v>8.498715490767958E-05</v>
+        <v>8.498715490768032E-05</v>
       </c>
       <c r="AR69">
-        <v>8.358962532980018E-05</v>
+        <v>8.358962532980165E-05</v>
       </c>
       <c r="AS69">
         <v>0</v>
@@ -95902,16 +95902,16 @@
         <v>0.002590040995281101</v>
       </c>
       <c r="Y76">
-        <v>0.002590040995281102</v>
+        <v>0.002590040995281101</v>
       </c>
       <c r="Z76">
-        <v>0.002590040995281102</v>
+        <v>0.002590040995281101</v>
       </c>
       <c r="AA76">
         <v>0.002590040995281102</v>
       </c>
       <c r="AB76">
-        <v>0.002590040995281102</v>
+        <v>0.002590040995281101</v>
       </c>
       <c r="AC76">
         <v>0.002590040995281102</v>
@@ -95923,13 +95923,13 @@
         <v>0.002590040995281102</v>
       </c>
       <c r="AF76">
-        <v>0.002590040995281102</v>
+        <v>0.002590040995281101</v>
       </c>
       <c r="AG76">
-        <v>0.002590040995281102</v>
+        <v>0.002590040995281101</v>
       </c>
       <c r="AH76">
-        <v>0.002590040995281102</v>
+        <v>0.002590040995281101</v>
       </c>
       <c r="AI76">
         <v>0.002590040995281102</v>
@@ -95938,13 +95938,13 @@
         <v>0.002590040995281102</v>
       </c>
       <c r="AK76">
-        <v>0.002590040995281102</v>
+        <v>0.002590040995281101</v>
       </c>
       <c r="AL76">
         <v>0.002590040995281102</v>
       </c>
       <c r="AM76">
-        <v>0.002590040995281101</v>
+        <v>0.002590040995281102</v>
       </c>
       <c r="AN76">
         <v>0.002590040995281101</v>
@@ -95953,16 +95953,16 @@
         <v>0.002590040995281102</v>
       </c>
       <c r="AP76">
-        <v>0.002590040995281102</v>
+        <v>0.002590040995281101</v>
       </c>
       <c r="AQ76">
         <v>0.002590040995281102</v>
       </c>
       <c r="AR76">
-        <v>0.002590040995281101</v>
+        <v>0.002590040995281102</v>
       </c>
       <c r="AS76">
-        <v>0.002585712939752126</v>
+        <v>0.002585712939752125</v>
       </c>
     </row>
     <row r="77" spans="1:45">
@@ -105795,49 +105795,49 @@
         <v>0.01831019146633582</v>
       </c>
       <c r="AE155">
-        <v>0.01867178510509904</v>
+        <v>0.01867178510509905</v>
       </c>
       <c r="AF155">
-        <v>0.01902436340379274</v>
+        <v>0.01902436340379275</v>
       </c>
       <c r="AG155">
-        <v>0.01936755535289703</v>
+        <v>0.01936755535289705</v>
       </c>
       <c r="AH155">
-        <v>0.01970111426545258</v>
+        <v>0.01970111426545259</v>
       </c>
       <c r="AI155">
-        <v>0.02002489882831162</v>
+        <v>0.02002489882831163</v>
       </c>
       <c r="AJ155">
-        <v>0.02033885699981143</v>
+        <v>0.02033885699981144</v>
       </c>
       <c r="AK155">
-        <v>0.02064301233429183</v>
+        <v>0.02064301233429184</v>
       </c>
       <c r="AL155">
-        <v>0.02093745237503161</v>
+        <v>0.02093745237503162</v>
       </c>
       <c r="AM155">
-        <v>0.02122231880947439</v>
+        <v>0.0212223188094744</v>
       </c>
       <c r="AN155">
-        <v>0.02149782713452609</v>
+        <v>0.0214978271345261</v>
       </c>
       <c r="AO155">
-        <v>0.02176428334486393</v>
+        <v>0.02176428334486394</v>
       </c>
       <c r="AP155">
-        <v>0.02202185371833643</v>
+        <v>0.02202185371833644</v>
       </c>
       <c r="AQ155">
-        <v>0.02227073726194119</v>
+        <v>0.02227073726194121</v>
       </c>
       <c r="AR155">
-        <v>0.02251116036775425</v>
+        <v>0.02251116036775426</v>
       </c>
       <c r="AS155">
-        <v>0.02274337230046682</v>
+        <v>0.02274337230046684</v>
       </c>
     </row>
     <row r="156" spans="1:45">
